--- a/evaluations/count/population_counting_results_ensamble_global_embedding.xlsx
+++ b/evaluations/count/population_counting_results_ensamble_global_embedding.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,31 @@
           <t>Ground Truth</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Use Fisher</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Embedding Model</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Global Weight</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Fisher Weight</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -647,6 +672,11 @@
       <c r="Z2" t="n">
         <v>182</v>
       </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -735,11 +765,16 @@
       <c r="Z3" t="n">
         <v>182</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BelugaID</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -751,32 +786,30 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="G4" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="H4" t="n">
-        <v>3175</v>
+        <v>412</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>830</v>
+        <v>353</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="b">
         <v>1</v>
       </c>
@@ -784,44 +817,53 @@
         <v>256</v>
       </c>
       <c r="O4" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P4" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="b">
         <v>1</v>
       </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>4135.51</v>
+        <v>408.64</v>
       </c>
       <c r="X4" t="n">
-        <v>113.6</v>
+        <v>106.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>106.17</v>
+        <v>58.72</v>
       </c>
       <c r="Z4" t="n">
-        <v>788</v>
+        <v>182</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -851,13 +893,13 @@
         <v>562500</v>
       </c>
       <c r="H5" t="n">
-        <v>2985</v>
+        <v>3175</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>808</v>
+        <v>830</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -900,22 +942,27 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>4184.5</v>
+        <v>4135.51</v>
       </c>
       <c r="X5" t="n">
-        <v>113.8</v>
+        <v>113.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>101.95</v>
+        <v>106.17</v>
       </c>
       <c r="Z5" t="n">
         <v>788</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>BelugaID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -939,13 +986,13 @@
         <v>562500</v>
       </c>
       <c r="H6" t="n">
-        <v>37731</v>
+        <v>2985</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>34203</v>
+        <v>808</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -984,21 +1031,26 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>28.37</v>
+        <v>4184.5</v>
       </c>
       <c r="X6" t="n">
-        <v>1.4</v>
+        <v>113.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>121.09</v>
+        <v>101.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
-      </c>
+        <v>788</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1027,13 +1079,13 @@
         <v>562500</v>
       </c>
       <c r="H7" t="n">
-        <v>37189</v>
+        <v>37731</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>33665</v>
+        <v>34203</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -1076,22 +1128,27 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>28.57</v>
+        <v>28.37</v>
       </c>
       <c r="X7" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>120.16</v>
+        <v>121.09</v>
       </c>
       <c r="Z7" t="n">
         <v>13</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HyenaID2022</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1115,13 +1172,13 @@
         <v>562500</v>
       </c>
       <c r="H8" t="n">
-        <v>1151</v>
+        <v>37189</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>977</v>
+        <v>33665</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -1160,26 +1217,31 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>1520.48</v>
+        <v>28.57</v>
       </c>
       <c r="X8" t="n">
-        <v>39.32</v>
+        <v>1.32</v>
       </c>
       <c r="Y8" t="n">
-        <v>87.01000000000001</v>
+        <v>120.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>256</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>HyenaID2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1203,13 +1265,13 @@
         <v>562500</v>
       </c>
       <c r="H9" t="n">
-        <v>4509</v>
+        <v>1151</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1825</v>
+        <v>977</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1252,17 +1314,22 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>2005.43</v>
+        <v>1520.48</v>
       </c>
       <c r="X9" t="n">
-        <v>82.08</v>
+        <v>39.32</v>
       </c>
       <c r="Y9" t="n">
-        <v>136.53</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>50</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1291,13 +1358,13 @@
         <v>562500</v>
       </c>
       <c r="H10" t="n">
-        <v>4338</v>
+        <v>4509</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1658</v>
+        <v>1825</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1340,22 +1407,27 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>2137.7</v>
+        <v>2005.43</v>
       </c>
       <c r="X10" t="n">
-        <v>84.38</v>
+        <v>82.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>136.35</v>
+        <v>136.53</v>
       </c>
       <c r="Z10" t="n">
         <v>50</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>IPanda50</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1379,13 +1451,13 @@
         <v>562500</v>
       </c>
       <c r="H11" t="n">
-        <v>4873</v>
+        <v>4338</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3792</v>
+        <v>1658</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1428,17 +1500,22 @@
         </is>
       </c>
       <c r="W11" t="n">
-        <v>443.71</v>
+        <v>2137.7</v>
       </c>
       <c r="X11" t="n">
-        <v>15.83</v>
+        <v>84.38</v>
       </c>
       <c r="Y11" t="n">
-        <v>112.25</v>
+        <v>136.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>237</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1473,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3796</v>
+        <v>3792</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1516,22 +1593,27 @@
         </is>
       </c>
       <c r="W12" t="n">
-        <v>448.78</v>
+        <v>443.71</v>
       </c>
       <c r="X12" t="n">
-        <v>16.15</v>
+        <v>15.83</v>
       </c>
       <c r="Y12" t="n">
-        <v>111.71</v>
+        <v>112.25</v>
       </c>
       <c r="Z12" t="n">
         <v>237</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1555,13 +1637,13 @@
         <v>562500</v>
       </c>
       <c r="H13" t="n">
-        <v>7492</v>
+        <v>4873</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2709</v>
+        <v>3796</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -1604,17 +1686,22 @@
         </is>
       </c>
       <c r="W13" t="n">
-        <v>534.27</v>
+        <v>448.78</v>
       </c>
       <c r="X13" t="n">
-        <v>17.13</v>
+        <v>16.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>91.29000000000001</v>
+        <v>111.71</v>
       </c>
       <c r="Z13" t="n">
-        <v>57</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1643,13 +1730,13 @@
         <v>562500</v>
       </c>
       <c r="H14" t="n">
-        <v>7457</v>
+        <v>7492</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2718</v>
+        <v>2709</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1692,17 +1779,115 @@
         </is>
       </c>
       <c r="W14" t="n">
-        <v>565.79</v>
+        <v>534.27</v>
       </c>
       <c r="X14" t="n">
-        <v>18.47</v>
+        <v>17.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>91.15000000000001</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="Z14" t="n">
         <v>57</v>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>750</v>
+      </c>
+      <c r="E15" t="n">
+        <v>750</v>
+      </c>
+      <c r="F15" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G15" t="n">
+        <v>562500</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7457</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2718</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>256</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>565.79</v>
+      </c>
+      <c r="X15" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/evaluations/count/population_counting_results_ensamble_global_embedding.xlsx
+++ b/evaluations/count/population_counting_results_ensamble_global_embedding.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,7 +623,7 @@
       <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="L2" t="b">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="b">
@@ -649,10 +649,10 @@
       <c r="S2" t="b">
         <v>1</v>
       </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
@@ -693,32 +693,30 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="G3" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="H3" t="n">
-        <v>14982</v>
+        <v>412</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>12418</v>
+        <v>353</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="b">
         <v>1</v>
       </c>
@@ -726,50 +724,54 @@
         <v>256</v>
       </c>
       <c r="O3" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="b">
         <v>1</v>
       </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>230.61</v>
+        <v>408.64</v>
       </c>
       <c r="X3" t="n">
-        <v>21.55</v>
+        <v>106.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>102.61</v>
+        <v>58.72</v>
       </c>
       <c r="Z3" t="n">
         <v>182</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -786,30 +788,32 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>750</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>750</v>
       </c>
       <c r="F4" t="n">
-        <v>2500</v>
+        <v>562500</v>
       </c>
       <c r="G4" t="n">
-        <v>2500</v>
+        <v>562500</v>
       </c>
       <c r="H4" t="n">
-        <v>412</v>
+        <v>14982</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>12418</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
@@ -817,59 +821,55 @@
         <v>256</v>
       </c>
       <c r="O4" t="n">
-        <v>2000000</v>
+        <v>7000000000</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="b">
         <v>1</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="W4" t="n">
-        <v>408.64</v>
+        <v>230.61</v>
       </c>
       <c r="X4" t="n">
-        <v>106.38</v>
+        <v>21.55</v>
       </c>
       <c r="Y4" t="n">
-        <v>58.72</v>
+        <v>102.61</v>
       </c>
       <c r="Z4" t="n">
         <v>182</v>
       </c>
-      <c r="AA4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>WildlifeReID10k</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BelugaID</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -881,88 +881,86 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E5" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="F5" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="G5" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="H5" t="n">
-        <v>3175</v>
+        <v>8619</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>830</v>
+        <v>7113</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>256</v>
       </c>
       <c r="O5" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P5" t="n">
-        <v>0.95</v>
+        <v>0.995</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="b">
         <v>1</v>
       </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>4135.51</v>
+        <v>324.14</v>
       </c>
       <c r="X5" t="n">
-        <v>113.6</v>
+        <v>25.56</v>
       </c>
       <c r="Y5" t="n">
-        <v>106.17</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>788</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BelugaID</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -974,32 +972,30 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E6" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="F6" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="G6" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="H6" t="n">
-        <v>2985</v>
+        <v>9313</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>808</v>
+        <v>7919</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="b">
         <v>1</v>
       </c>
@@ -1007,55 +1003,59 @@
         <v>256</v>
       </c>
       <c r="O6" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="b">
         <v>1</v>
       </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>4184.5</v>
+        <v>416.83</v>
       </c>
       <c r="X6" t="n">
-        <v>113.8</v>
+        <v>36.71</v>
       </c>
       <c r="Y6" t="n">
-        <v>101.95</v>
+        <v>15.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>788</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1067,32 +1067,30 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E7" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="F7" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="G7" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="H7" t="n">
-        <v>37731</v>
+        <v>8619</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>34203</v>
+        <v>7308</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="b">
         <v>1</v>
       </c>
@@ -1100,55 +1098,59 @@
         <v>256</v>
       </c>
       <c r="O7" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P7" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="b">
         <v>1</v>
       </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>28.37</v>
+        <v>376.78</v>
       </c>
       <c r="X7" t="n">
-        <v>1.4</v>
+        <v>31.72</v>
       </c>
       <c r="Y7" t="n">
-        <v>121.09</v>
+        <v>15.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1160,32 +1162,30 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E8" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="F8" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="G8" t="n">
-        <v>562500</v>
+        <v>62500</v>
       </c>
       <c r="H8" t="n">
-        <v>37189</v>
+        <v>9394</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>33665</v>
+        <v>7892</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="b">
         <v>1</v>
       </c>
@@ -1193,55 +1193,59 @@
         <v>256</v>
       </c>
       <c r="O8" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P8" t="n">
-        <v>0.95</v>
+        <v>0.995</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="b">
         <v>1</v>
       </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>28.57</v>
+        <v>366.97</v>
       </c>
       <c r="X8" t="n">
-        <v>1.32</v>
+        <v>29.18</v>
       </c>
       <c r="Y8" t="n">
-        <v>120.16</v>
+        <v>14.58</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HyenaID2022</t>
+          <t>BelugaID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1265,18 +1269,18 @@
         <v>562500</v>
       </c>
       <c r="H9" t="n">
-        <v>1151</v>
+        <v>3175</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>977</v>
+        <v>830</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
-      <c r="L9" t="b">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="b">
@@ -1302,10 +1306,10 @@
       <c r="S9" t="b">
         <v>1</v>
       </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="b">
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
@@ -1314,16 +1318,16 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>1520.48</v>
+        <v>4135.51</v>
       </c>
       <c r="X9" t="n">
-        <v>39.32</v>
+        <v>113.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>87.01000000000001</v>
+        <v>106.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>256</v>
+        <v>788</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
@@ -1334,7 +1338,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>BelugaID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1358,18 +1362,18 @@
         <v>562500</v>
       </c>
       <c r="H10" t="n">
-        <v>4509</v>
+        <v>2985</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1825</v>
+        <v>808</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
-      <c r="L10" t="b">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="b">
@@ -1395,10 +1399,10 @@
       <c r="S10" t="b">
         <v>1</v>
       </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
@@ -1407,16 +1411,16 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>2005.43</v>
+        <v>4184.5</v>
       </c>
       <c r="X10" t="n">
-        <v>82.08</v>
+        <v>113.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>136.53</v>
+        <v>101.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>788</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
@@ -1427,7 +1431,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IPanda50</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1451,18 +1455,18 @@
         <v>562500</v>
       </c>
       <c r="H11" t="n">
-        <v>4338</v>
+        <v>37189</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1658</v>
+        <v>33665</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
-      <c r="L11" t="b">
+      <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="b">
@@ -1488,28 +1492,28 @@
       <c r="S11" t="b">
         <v>1</v>
       </c>
-      <c r="T11" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" t="b">
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>2137.7</v>
+        <v>28.57</v>
       </c>
       <c r="X11" t="n">
-        <v>84.38</v>
+        <v>1.32</v>
       </c>
       <c r="Y11" t="n">
-        <v>136.35</v>
+        <v>120.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
@@ -1520,7 +1524,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1544,18 +1548,18 @@
         <v>562500</v>
       </c>
       <c r="H12" t="n">
-        <v>4873</v>
+        <v>37731</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3792</v>
+        <v>34203</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
-      <c r="L12" t="b">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="b">
@@ -1581,28 +1585,28 @@
       <c r="S12" t="b">
         <v>1</v>
       </c>
-      <c r="T12" t="b">
-        <v>0</v>
-      </c>
-      <c r="U12" t="b">
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>443.71</v>
+        <v>28.37</v>
       </c>
       <c r="X12" t="n">
-        <v>15.83</v>
+        <v>1.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>112.25</v>
+        <v>121.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>237</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
@@ -1613,7 +1617,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>HyenaID2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1637,18 +1641,18 @@
         <v>562500</v>
       </c>
       <c r="H13" t="n">
-        <v>4873</v>
+        <v>1151</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3796</v>
+        <v>977</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
-      <c r="L13" t="b">
+      <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="b">
@@ -1674,10 +1678,10 @@
       <c r="S13" t="b">
         <v>1</v>
       </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" t="b">
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
@@ -1686,16 +1690,16 @@
         </is>
       </c>
       <c r="W13" t="n">
-        <v>448.78</v>
+        <v>1520.48</v>
       </c>
       <c r="X13" t="n">
-        <v>16.15</v>
+        <v>39.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>111.71</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
@@ -1706,7 +1710,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>IPanda50</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1730,18 +1734,18 @@
         <v>562500</v>
       </c>
       <c r="H14" t="n">
-        <v>7492</v>
+        <v>4509</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2709</v>
+        <v>1825</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
-      <c r="L14" t="b">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="b">
@@ -1767,10 +1771,10 @@
       <c r="S14" t="b">
         <v>1</v>
       </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" t="b">
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
@@ -1779,16 +1783,16 @@
         </is>
       </c>
       <c r="W14" t="n">
-        <v>534.27</v>
+        <v>2005.43</v>
       </c>
       <c r="X14" t="n">
-        <v>17.13</v>
+        <v>82.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>91.29000000000001</v>
+        <v>136.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
@@ -1799,7 +1803,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>IPanda50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1823,18 +1827,18 @@
         <v>562500</v>
       </c>
       <c r="H15" t="n">
-        <v>7457</v>
+        <v>4338</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2718</v>
+        <v>1658</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
-      <c r="L15" t="b">
+      <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="b">
@@ -1860,10 +1864,10 @@
       <c r="S15" t="b">
         <v>1</v>
       </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" t="b">
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
@@ -1872,16 +1876,16 @@
         </is>
       </c>
       <c r="W15" t="n">
-        <v>565.79</v>
+        <v>2137.7</v>
       </c>
       <c r="X15" t="n">
-        <v>18.47</v>
+        <v>84.38</v>
       </c>
       <c r="Y15" t="n">
-        <v>91.15000000000001</v>
+        <v>136.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
@@ -1889,6 +1893,378 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>750</v>
+      </c>
+      <c r="E16" t="n">
+        <v>750</v>
+      </c>
+      <c r="F16" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G16" t="n">
+        <v>562500</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4873</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3792</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>256</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>443.71</v>
+      </c>
+      <c r="X16" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>237</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>750</v>
+      </c>
+      <c r="E17" t="n">
+        <v>750</v>
+      </c>
+      <c r="F17" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G17" t="n">
+        <v>562500</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4873</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3796</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>256</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>448.78</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>111.71</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>237</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>750</v>
+      </c>
+      <c r="E18" t="n">
+        <v>750</v>
+      </c>
+      <c r="F18" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G18" t="n">
+        <v>562500</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7492</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2709</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>256</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>534.27</v>
+      </c>
+      <c r="X18" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" t="n">
+        <v>750</v>
+      </c>
+      <c r="F19" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G19" t="n">
+        <v>562500</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7457</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2718</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>256</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>565.79</v>
+      </c>
+      <c r="X19" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/evaluations/count/population_counting_results_ensamble_global_embedding.xlsx
+++ b/evaluations/count/population_counting_results_ensamble_global_embedding.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C2" t="b">
+      <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
@@ -689,7 +689,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C3" t="b">
+      <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
@@ -784,7 +784,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
@@ -877,7 +877,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C5" t="b">
+      <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
@@ -944,11 +944,7 @@
       <c r="AA5" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
@@ -968,7 +964,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C6" t="b">
+      <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
@@ -1063,7 +1059,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C7" t="b">
+      <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
@@ -1158,7 +1154,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C8" t="b">
+      <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
@@ -1253,7 +1249,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C9" t="b">
+      <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
@@ -1346,7 +1342,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C10" t="b">
+      <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
@@ -1439,7 +1435,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C11" t="b">
+      <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
@@ -1532,7 +1528,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C12" t="b">
+      <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
@@ -1625,7 +1621,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C13" t="b">
+      <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
@@ -1718,7 +1714,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C14" t="b">
+      <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
@@ -1811,7 +1807,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C15" t="b">
+      <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
@@ -1904,7 +1900,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C16" t="b">
+      <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
@@ -1997,7 +1993,7 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C17" t="b">
+      <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
@@ -2082,7 +2078,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2090,36 +2086,32 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C18" t="b">
-        <v>0</v>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="G18" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="H18" t="n">
-        <v>7492</v>
+        <v>126</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J18" t="n">
-        <v>2709</v>
+        <v>14</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="b">
         <v>1</v>
       </c>
@@ -2127,7 +2119,7 @@
         <v>256</v>
       </c>
       <c r="O18" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P18" t="n">
         <v>0.95</v>
@@ -2137,45 +2129,49 @@
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="b">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>534.27</v>
+        <v>1561.06</v>
       </c>
       <c r="X18" t="n">
-        <v>17.13</v>
+        <v>99.92</v>
       </c>
       <c r="Y18" t="n">
-        <v>91.29000000000001</v>
+        <v>80.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2183,36 +2179,32 @@
           <t>ensamble</t>
         </is>
       </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="G19" t="n">
-        <v>562500</v>
+        <v>2500</v>
       </c>
       <c r="H19" t="n">
-        <v>7457</v>
+        <v>883</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="J19" t="n">
-        <v>2718</v>
+        <v>46</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="b">
         <v>1</v>
       </c>
@@ -2220,7 +2212,7 @@
         <v>256</v>
       </c>
       <c r="O19" t="n">
-        <v>7000000000</v>
+        <v>2000000</v>
       </c>
       <c r="P19" t="n">
         <v>0.95</v>
@@ -2230,40 +2222,509 @@
           <t>RANSAC</t>
         </is>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="b">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>1030.33</v>
+      </c>
+      <c r="X19" t="n">
+        <v>127.58</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>237</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>538</v>
+      </c>
+      <c r="I20" t="n">
+        <v>538</v>
+      </c>
+      <c r="J20" t="n">
+        <v>49</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>256</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>1338.92</v>
+      </c>
+      <c r="X20" t="n">
+        <v>89.61</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>237</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" t="n">
+        <v>200</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2947</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2947</v>
+      </c>
+      <c r="J21" t="n">
+        <v>115</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>256</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>807.7</v>
+      </c>
+      <c r="X21" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>237</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" t="n">
+        <v>500</v>
+      </c>
+      <c r="F22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>937</v>
+      </c>
+      <c r="I22" t="n">
+        <v>937</v>
+      </c>
+      <c r="J22" t="n">
+        <v>61</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>256</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>1456.27</v>
+      </c>
+      <c r="X22" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>237</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>750</v>
+      </c>
+      <c r="E23" t="n">
+        <v>750</v>
+      </c>
+      <c r="F23" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G23" t="n">
+        <v>562500</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7492</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2709</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>256</v>
+      </c>
+      <c r="O23" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="W19" t="n">
+      <c r="W23" t="n">
+        <v>534.27</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>750</v>
+      </c>
+      <c r="E24" t="n">
+        <v>750</v>
+      </c>
+      <c r="F24" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G24" t="n">
+        <v>562500</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7457</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2718</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>256</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
         <v>565.79</v>
       </c>
-      <c r="X19" t="n">
+      <c r="X24" t="n">
         <v>18.47</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y24" t="n">
         <v>91.15000000000001</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z24" t="n">
         <v>57</v>
       </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
